--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2542-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2542-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99C4DA86-E339-4E9D-B017-3C0E771ED0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC12730C-607B-48DA-BC0D-914352ECA647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{5ABD1F09-41AE-4A54-BDE2-1984FAF45C3A}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{E6999520-C114-4EAC-BB7B-420B48968208}"/>
   </bookViews>
   <sheets>
     <sheet name="2542-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1508,26 +1508,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03949B41-01FD-4DFD-A13E-C151073A66EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A252A7B-9612-4599-8D9F-4E6205F11082}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1561,7 +1561,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1597,7 +1597,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1717,7 +1717,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2021</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2020</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2019</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>33</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>6.09</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>33</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>33</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2018</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2017</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>8.48</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2016</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2015</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2014</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2013</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2012</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>5.46</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2011</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>7.31</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2010</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2009</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2008</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2007</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2006</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2005</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>8.42</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2004</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>8.15</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2003</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2002</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2001</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2000</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>43.2</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>1999</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>1998</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>1997</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>1996</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>1995</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35" t="s">
         <v>57</v>
       </c>
